--- a/resources/templates/ImportTemplate_typical.xlsx
+++ b/resources/templates/ImportTemplate_typical.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workdir\DeerHide\sources\jira-toolkit\resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8892B9DF-5547-4045-9242-4F78BEBD82F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3236045-3B1B-4AA4-A5FD-666151BFADFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="31785" activeTab="1" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
+    <workbookView xWindow="8430" yWindow="5325" windowWidth="43200" windowHeight="23445" xr2:uid="{1FA076D1-0294-4A97-AB8C-3ADE2BC9CEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -1847,8 +1847,8 @@
     <col min="1" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.28515625" customWidth="1"/>
+    <col min="5" max="5" width="51.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
@@ -2757,15 +2757,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c471fd26-9765-4fbe-b6fd-c17c1e55c974">
@@ -2774,6 +2765,15 @@
     <TaxCatchAll xmlns="9df69692-83aa-4c55-88c1-62abad05f4fe" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3006,20 +3006,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFE630F-6530-4863-AB67-8477539A0000}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c471fd26-9765-4fbe-b6fd-c17c1e55c974"/>
     <ds:schemaRef ds:uri="9df69692-83aa-4c55-88c1-62abad05f4fe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{156C3F15-3876-4FBB-8F24-692088DE8D9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
